--- a/server/src/Pos.Server.Host/Assets/Reports/ShiftReport.xlsx
+++ b/server/src/Pos.Server.Host/Assets/Reports/ShiftReport.xlsx
@@ -63,7 +63,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -85,11 +85,55 @@
         <color rgb="00808080"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00808080"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00808080"/>
+      </right>
+      <top style="thin">
+        <color rgb="00808080"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00808080"/>
+      </right>
+      <top style="thin">
+        <color rgb="00808080"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00808080"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00808080"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00808080"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -111,6 +155,8 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -505,7 +551,7 @@
           <t>{{StoreName}}</t>
         </is>
       </c>
-      <c r="C3" s="4" t="n"/>
+      <c r="C3" s="9" t="n"/>
       <c r="D3" s="2" t="inlineStr">
         <is>
           <t>端末</t>
@@ -516,7 +562,7 @@
           <t>{{TerminalName}}</t>
         </is>
       </c>
-      <c r="F3" s="4" t="n"/>
+      <c r="F3" s="9" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -529,7 +575,7 @@
           <t>{{BusinessDate}}</t>
         </is>
       </c>
-      <c r="C4" s="4" t="n"/>
+      <c r="C4" s="9" t="n"/>
       <c r="D4" s="2" t="inlineStr">
         <is>
           <t>状態</t>
@@ -540,7 +586,7 @@
           <t>{{Status}}</t>
         </is>
       </c>
-      <c r="F4" s="4" t="n"/>
+      <c r="F4" s="9" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -553,7 +599,7 @@
           <t>{{OpenedAt}}</t>
         </is>
       </c>
-      <c r="C5" s="4" t="n"/>
+      <c r="C5" s="9" t="n"/>
       <c r="D5" s="2" t="inlineStr">
         <is>
           <t>開設担当</t>
@@ -564,7 +610,7 @@
           <t>{{OpenedBy}}</t>
         </is>
       </c>
-      <c r="F5" s="4" t="n"/>
+      <c r="F5" s="9" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -577,7 +623,7 @@
           <t>{{ClosedAt}}</t>
         </is>
       </c>
-      <c r="C6" s="4" t="n"/>
+      <c r="C6" s="9" t="n"/>
       <c r="D6" s="2" t="inlineStr">
         <is>
           <t>精算担当</t>
@@ -588,7 +634,7 @@
           <t>{{ClosedBy}}</t>
         </is>
       </c>
-      <c r="F6" s="4" t="n"/>
+      <c r="F6" s="9" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -601,7 +647,7 @@
           <t>{{IssuedAt}}</t>
         </is>
       </c>
-      <c r="C7" s="4" t="n"/>
+      <c r="C7" s="9" t="n"/>
     </row>
     <row r="9" ht="20" customHeight="1">
       <c r="A9" s="5" t="inlineStr">
@@ -628,12 +674,12 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>予想現金</t>
+          <t>前受金受取</t>
         </is>
       </c>
       <c r="E10" s="7" t="inlineStr">
         <is>
-          <t>{{ExpectedCash}}</t>
+          <t>{{DepositCashIn}}</t>
         </is>
       </c>
     </row>
@@ -650,12 +696,12 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>実査金額</t>
+          <t>前受金返金</t>
         </is>
       </c>
       <c r="E11" s="7" t="inlineStr">
         <is>
-          <t>{{ActualCash}}</t>
+          <t>{{DepositCashOut}}</t>
         </is>
       </c>
     </row>
@@ -672,12 +718,12 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>過不足</t>
+          <t>予想現金</t>
         </is>
       </c>
       <c r="E12" s="7" t="inlineStr">
         <is>
-          <t>{{Difference}}</t>
+          <t>{{ExpectedCash}}</t>
         </is>
       </c>
     </row>
@@ -692,6 +738,16 @@
           <t>{{PaidIn}}</t>
         </is>
       </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>実査金額</t>
+        </is>
+      </c>
+      <c r="E13" s="7" t="inlineStr">
+        <is>
+          <t>{{ActualCash}}</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -702,6 +758,16 @@
       <c r="B14" s="7" t="inlineStr">
         <is>
           <t>{{PaidOut}}</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>過不足</t>
+        </is>
+      </c>
+      <c r="E14" s="7" t="inlineStr">
+        <is>
+          <t>{{Difference}}</t>
         </is>
       </c>
     </row>
@@ -1030,10 +1096,10 @@
           <t>{{Note}}</t>
         </is>
       </c>
-      <c r="C38" s="4" t="n"/>
-      <c r="D38" s="4" t="n"/>
-      <c r="E38" s="4" t="n"/>
-      <c r="F38" s="4" t="n"/>
+      <c r="C38" s="10" t="n"/>
+      <c r="D38" s="10" t="n"/>
+      <c r="E38" s="10" t="n"/>
+      <c r="F38" s="9" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="11">
